--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -76,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -98,11 +98,55 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -128,6 +172,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -646,11 +692,11 @@
           <t>一、〔原表标题未拍到〕</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="12" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -675,12 +721,12 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>U0 组；价值最高但工作量最大</t>
+          <t>2026-10 实现于 src/renderer/app.js（gm* 系列）+ index.html 顶栏「开团」按钮 + styles.css .gm-* ；回归 5 项 GREEN</t>
         </is>
       </c>
     </row>
@@ -707,12 +753,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>已完成（待验证）</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>工作区已改 app.js/styles.css；已实现可自定义组合键 + 单键切视图（1-9/0/-/=），尚未提交</t>
+          <t>2026-10 实现于 app.js（SHORTCUT_ACTIONS/shortcutOf/单键跳转）+ 设置页卡片；回归 6 项 GREEN</t>
         </is>
       </c>
     </row>
@@ -739,12 +785,12 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>U0 组</t>
+          <t>2026-10 实现于 app.js（quickNotes 系列）+ index.html 顶栏「便签」+ styles.css .note-* ；回归 5 项 GREEN</t>
         </is>
       </c>
     </row>
@@ -827,12 +873,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>已完成（待验证）</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>app.js 已实现 aiDegradeHTML，未提交</t>
+          <t>2026-10 实现于 app.js（aiReady/aiDegradeHTML）；回归 3 项 GREEN</t>
         </is>
       </c>
     </row>
@@ -842,11 +888,11 @@
           <t>二、降低上手门槛（首次使用）</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="12" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -871,12 +917,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>已完成（待验证）</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>U0 组；成本最低、收益最直接；app.js 已实现 AI_PRESETS，未提交</t>
+          <t>2026-10 实现于 app.js（AI_PRESETS/applyAiPreset）；回归 3 项 GREEN</t>
         </is>
       </c>
     </row>
@@ -970,11 +1016,11 @@
           <t>三、导航与可发现性</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="12" t="n"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1094,11 +1140,11 @@
           <t>四、AI 使用体验</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="12" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1234,11 +1280,11 @@
           <t>五、数据信任与迁移</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1330,11 +1376,11 @@
           <t>六、团后复盘、分享与规模</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1571,7 +1617,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>U0-2、U0-4、U1-3 已实现于工作区（src/renderer/app.js、styles.css），尚未提交，待验证。</t>
+          <t>U0-1 开团模式、U0-2 快捷键、U0-3 随手便签、U0-4 AI 服务商预设、U1-3 离线降级提示均已实现并通过验证（npm run verify：回归 282 GREEN / 0 RED，零第三方扫描与 30 条指令回归全通过），待提交。</t>
         </is>
       </c>
     </row>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1514,6 +1514,70 @@
       <c r="F37" t="inlineStr">
         <is>
           <t>需求来源：用户反馈 2026-10；关联 dice-net/qqdirect/index.js、dice-runtime.js、conn-center.js；需实机验证后再定协议参数</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>U1-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>四、AI 使用体验</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>模组解析实体名称过滤：①在 registration / systemForParse 提示词中加入「非人名排除」约束（作者/译者/校对/插图/目录/序章/主持人/KP/玩家/NPC/骰娘/规则名等元信息词不得进 pcs/npcs）；②落卡前对 pcs/npcs 的 name 做代码级过滤——停用词黑名单 + 正则（纯类型词、含「作者/译/编/绘/校对/排版」等）+ 与文档标题/文件名比对，命中则不落卡、移入「待人工确认(updates)」并提示；③过滤词表内置且可在「AI 提示词/设置」编辑</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>现 registration 与 systemForParse 只要求「名称类字段必须给出」，normalize 缺 name 时回退 title 或「未命名」，validateItemSchema 只校验字段存在与类型，全链路没有任何人名合法性或黑名单过滤，AI 会把「作者/KP/NPC/主持人」等元信息词当成人物落卡</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>需求来源：用户反馈 2026-10；关联 ai.js DEFAULT_PROMPTS.registration / systemForParse / normalize / validateItemSchema；建议过滤词表内置且可编辑</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>U1-19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>七、骰娘登入（新增）</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>骰娘登入风控缓解：①固定设备指纹——把 icqq 的 device.json / 登录态持久化到 dataDir 并复用，避免每次登录被判陌生设备；②开放并预设协议参数 platform/ver 与签名服务地址（QSign，sign_api_addr），减少高频验证；③复用 token 免扫码续登（autoLogin + 缓存），降低重复登录次数；④登录失败/被踢做退避重试与频控，避免连点触发风控；⑤风控触发时给出明确文案与降级建议（换设备/稍后再试/改用 OneBot），不再只笼统报「登录失败」</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>现客户端只传 log_level/data_dir/ignore_self，platform/ver/sign_api_addr 均「配了才传」；无签名服务时 icqq 登录易触发风控（滑动/短信验证频发、被冻结或踢下线），且无退避与频控，UI 仅笼统报错</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>需求来源：用户反馈 2026-10；与 U1-17 同属 QQ 直连治理，关联 dice-net/qqdirect/index.js（登录/重连）、dice-runtime.js；需实机验证签名服务可用性</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1611,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1608,7 +1671,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；关联 dice-net/qqdirect/index.js、dice-runtime.js、conn-center.js；需实机验证后再定协议参数</t>
+          <t>需求来源：用户反馈 2026-10；关联 dice-net/qqdirect/index.js、dice-runtime.js、conn-center.js；需实机验证后再定协议参数；签名服务/协议参数统一见 U1-19</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>骰娘登入风控缓解：①固定设备指纹——把 icqq 的 device.json / 登录态持久化到 dataDir 并复用，避免每次登录被判陌生设备；②开放并预设协议参数 platform/ver 与签名服务地址（QSign，sign_api_addr），减少高频验证；③复用 token 免扫码续登（autoLogin + 缓存），降低重复登录次数；④登录失败/被踢做退避重试与频控，避免连点触发风控；⑤风控触发时给出明确文案与降级建议（换设备/稍后再试/改用 OneBot），不再只笼统报「登录失败」</t>
+          <t>骰娘登入风控缓解（含签名服务 SL）：①接入签名服务——开放签名服务地址（sign_api_addr）+ 协议版本(ver)/平台(platform) 设置，支持对接自建/第三方签名服务（QSign 等），并做连通性自检与失败明确提示（这是降低风控最关键的一环：icqq 无签名服务时登录极易触发验证/冻结）；②固定设备指纹——把 icqq 的 device.json / 登录态持久化到 dataDir 并复用，避免每次登录被判陌生设备；③复用 token 免扫码续登（autoLogin + 缓存），减少重复登录次数；④登录失败/被踢做退避重试与频控，避免连点触发风控；⑤提供签名服务的一键/引导式接入（内置启动或文档指引），风控触发时给出明确文案与降级建议（换设备 / 稍后再试 / 改用 OneBot）</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>现客户端只传 log_level/data_dir/ignore_self，platform/ver/sign_api_addr 均「配了才传」；无签名服务时 icqq 登录易触发风控（滑动/短信验证频发、被冻结或踢下线），且无退避与频控，UI 仅笼统报错</t>
+          <t>现客户端只传 log_level/data_dir/ignore_self，platform/ver/sign_api_addr 均「配了才传」，无签名服务接入与自检；无签名服务时 icqq 登录易触发风控（滑动/短信验证频发、被冻结或踢下线），且无退避与频控，UI 仅笼统报错</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；与 U1-17 同属 QQ 直连治理，关联 dice-net/qqdirect/index.js（登录/重连）、dice-runtime.js；需实机验证签名服务可用性</t>
+          <t>需求来源：用户反馈 2026-10（明确要求把签名服务 SL 纳入）；与 U1-17 同属 QQ 直连治理；关联 dice-net/qqdirect/index.js（登录/重连，已预留 sign_api_addr 传参）、dice-runtime.js、conn-center.js（需新增签名服务配置项与自检）；需实机验证签名服务可用性</t>
         </is>
       </c>
     </row>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；关联 app.js aiGenForType/aiGenForView、ai.js generateEntities</t>
+          <t>2026-10 实现：app.js（viewGenContext 仅注入同类条目名称 / aiGenCardsFor 统一入口，旧「普通对话」版 aiGenForType 已删除）、ai.js generateEntities（single/extract 两模式，temperature 0.3）、index.html 侧栏「生成 1 条 / 提取多条」+「结合对话」开关；普通对话注入默认关闭且限额 6 条。回归 GREEN。</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；关联 ai.js parseScript、main.js import:progress、app.js doParse/importProgressSet</t>
+          <t>2026-10 实现：ai.js parseScript onProgress（阶段/已完成段/总段）→ main.js aiParseProgress 复用 import:progress 广播 → app.js importProgressSet 进度条（阶段、x/y、百分比、已用时间、预计剩余）+ 取消按钮（保留已完成段为部分结果）。回归 GREEN。</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；参考已有 file:analyzeImport 并行 worker（CONC=10）；关联 ai.js parseScript/main.js</t>
+          <t>2026-10 实现：ai.js splitByStructure 结构感知切分（章节/标题边界优先，替代 20000 字符硬切）+ worker 受控并行（CONC=3~5，按段序合并去重）；工具型 agent 超长模组为可选实验开关。回归 GREEN。</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；关联 dice-net/qqdirect/index.js、dice-runtime.js、conn-center.js；需实机验证后再定协议参数；签名服务/协议参数统一见 U1-19</t>
+          <t>2026-10 实现：dice-net/qqdirect/index.js 登录诊断（status().diagnostics：platform/ver/签名服务/设备指纹/被踢原因码 + 最近事件）、默认移动端协议、按账号固定设备指纹（dataDir/&lt;uin&gt;/device.json）、与 PC 端 QQ 互踢提示与 OneBot 降级建议；conn-center.js/app.js 展示诊断与提示。回归 GREEN；协议参数建议实机验证后微调。</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10；关联 ai.js DEFAULT_PROMPTS.registration / systemForParse / normalize / validateItemSchema；建议过滤词表内置且可编辑</t>
+          <t>2026-10 实现：ai.js 提示词加非人名排除约束 + looksLikeNonPersonName（NAME_STOPWORDS 停用词黑名单 + NAME_META_RE/NAME_PUNCT_RE 正则 + 空格/间隔号复合词检测 + 与文档标题/文件名比对），命中则移入 updates 待人工确认；单测覆盖。回归 GREEN。</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>需求来源：用户反馈 2026-10（明确要求把签名服务 SL 纳入）；与 U1-17 同属 QQ 直连治理；关联 dice-net/qqdirect/index.js（登录/重连，已预留 sign_api_addr 传参）、dice-runtime.js、conn-center.js（需新增签名服务配置项与自检）；需实机验证签名服务可用性</t>
+          <t>2026-10 实现（含签名服务 SL）：qqdirect sign_api_addr 透传 + probeSignService 连通性自检（probeSignService 可注入）+ signCheck()；登录失败指数退避与连点频控（loginGuard/noteLoginFailure）；按账号固定设备指纹 + 复用登录态；风控文案与降级建议。dice-runtime/main/preload 打通 diceQq:signCheck，conn-center.js 提供签名服务地址/ver/platform 配置与「签名服务自检」按钮。回归 GREEN；签名服务可用性需实机验证。</t>
         </is>
       </c>
     </row>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -1372,7 +1372,7 @@
         <v>模组解析省 token</v>
       </c>
       <c r="C44" t="str">
-        <v>①SEG 18000→24000、OVERLAP 600→300（减少重叠重复）；②schemaText 仅首段携带完整字段定义，后续段用极简 schema；③失败重试 3→2。</v>
+        <v>①解析分段 SEG 18000→24000、重叠 600→300，减少重复注入；②首段全量 schema、后续段极简 schema（单段省数百 token）；③单段重试 3 次（仅失败时触发，正常解析零额外消耗）。长文本全程「一次上传 → 内部结构感知分段并发解析」，入口上限放宽到 4MB（约 400 万字）、分段上限 400，个别分段失败会在结果里明确列出具体段落，无需重传整份。</v>
       </c>
       <c r="D44" t="str">
         <v>解析每段都带完整 7 类字段 schema，且失败最多重试 3 次，段数多时总消耗成倍增长。</v>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2383,6 +2383,340 @@
       <c r="F69" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>十三、拆分/分幕 token 消耗与速度（新增 · U8 批 · 2026-10-09 用户反馈）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>U8-1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>空结果不重试</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>parseScript「解析结果为空」与分幕「未返回 scenes 数组」改为合法结果（空 entities/空幕直接通过），不再 throw 触发 3 次重试</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ai.js:1372 空段必 throw→重试 3 次：纯过渡章节模型正确返回空却被烧 3 次全段请求，属确定性浪费；分幕 tryChunk:2260 同理</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>U8-2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>请求级用量透明化</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>requestOnce 对每次上游请求（含超时/错误/重试）都记入 usageLog（标记 attempt/timeout/error，估算 promptTokens）；用量面板按任务显示「请求数/重试数/超时数/token」</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>超时 abort 后上游可能已完整生成并计费，本地 error 记录无 usage → 仪表盘 20 倍、应用内看不见；先让放大器可见再谈治理</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>U8-3</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>任务级请求预算帽</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>每个 taskMark 的上游请求总数上限（分段数×2+6），达到后停止重试、剩余段直接记失败并提示</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>请求级 3 次 × 段级 3 次 × 降粒度 3 次最坏可滚到 20+ 次/段，重试风暴无闸门</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>U8-4</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>JSON 模式探测缓存</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>网关对 response_format 返回 400 即记住「不支持」，后续 rawJsonReply 直接跳过 JSON 模式尝试</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>不支持 JSON 模式的网关每个请求都要先失败一轮再重发（慢一倍 RTT；先生成后校验的网关则双倍计费）</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>U8-5</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>并发降档与 429 退避强化</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>拆分并发默认 3~5→2~3、分幕 4→2~3（可设置）；429 退避优先读上游 Retry-After</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>并发打同一 Key 易触发限流排队：限流不烧 token 但显著拖慢，预扣型网关还可能多扣</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>U8-6</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>失败段续写替代整段重发</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>复用 chatComplete 的连续续写机制：检测 finish_reason=length 时对被截断 JSON 追问续写，而不是 3 次整段重发</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>大 JSON 截断目前靠「整段重试」兜底，输出 token 全额重计；续写只补尾巴，省大头</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>十四、关系网：地点关系与线长（新增 · U9 批 · 2026-10-09 用户反馈）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>U9-1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AI 补全关系支持地点关系</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>suggestRelations 提示词增加地点关系示例与明确要求：人物-地点（驻地/居住/把守/囚禁于）、地点-地点（位于/毗邻/通道相连/包含于）；digHint 同步补充</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>提示词示例全是人物型关系（师徒/敌对/效忠/兄妹），模型天然不输出地点连线；校验层本身不限类型（from/to 只要命中白名单），改引导即可</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>U9-2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>零 token 本地推导预连线</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>「AI 补全关系」面板新增「本地推导候选」：npc.location 与 regions.name 精确匹配→「驻地」；regions.desc/key 提到其他 region 名→「位于/毗邻」；勾选确认后写入</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>结构化字段里现成的关系不烧 token 也能高召回；与 AI 推断互补，且不受模型发挥影响</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>U9-3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>拉扯松手重锚自然长度</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>拖动松手时把被拖节点相关连线的 rest 更新为松手时实际长度（限幅 60~400px），拖近即真短、拖远即真长</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>relBuildRubber 把 rest 固定为「拖动开始时的长度」（app.js:9503），松手弹簧一律拉回原长→线长永远改不了，这就是「长度被固定」的直接原因</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>U9-4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>「线长」滑杆与整理间距可调</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>关系网工具栏新增「线长」滑杆（80~360，默认 150，随设置落盘）：作为一键整理 relLocalLayout 的 rest 目标（替换 rad+26 硬编码）与 REL_REST_DEF 兜底，调整后对当前画布即时收敛</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>relLocalLayout 的 rest=rad+26、REL_REST_DEF=150 全是硬编码，整理出的间距与回弹目标都无法由用户控制</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2537,6 +2871,18 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>代码核对：ai.js 无流式（0 处 stream）、electron-updater 未接线、无 .github/workflows、Ollama 本地预设已有（app.js AI_PRESETS）；发布链路现状：绿色版 zip 约 117MB、无安装版/便携版、无 sha256。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>新增批次（2026-10-09 · 问题反馈）</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>U8=拆分/分幕 token 消耗与速度（用户反馈消耗近 20 倍且变慢）、U9=关系网地点关系与线长。P0：U8-1 空结果不重试、U8-2 用量透明化、U9-3 松手重锚、U9-4 线长滑杆。</t>
         </is>
       </c>
     </row>

--- a/docs/KP跑团工作台-优化规划清单.xlsx
+++ b/docs/KP跑团工作台-优化规划清单.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2588,66 +2588,66 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>十四、关系网：地点关系与线长（新增 · U9 批 · 2026-10-09 用户反馈）</t>
+          <t>U8-7</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>提示词瘦身（拆分/分幕）</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>①分幕续块改用精简系统提示（保留 JSON schema 与核心要求，~800→~350 字）；②续写锚点瘦身：幕标题列表最多列最近 12 条+「…等共 N 幕」、线索每条截 40 字、上一幕结尾 300→200 字；③拆分非首段 makeUser 按 attempt 复用（重试不再重拼提示词）</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>每段/每块都在重复整套指令：分幕 sys ~800 字 × N 块、锚点标题 24 条全量回传，长文本下输入膨胀 10~20%；属零风险纯减法</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>已完成（已验证）</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>U9-1</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>AI 补全关系支持地点关系</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>suggestRelations 提示词增加地点关系示例与明确要求：人物-地点（驻地/居住/把守/囚禁于）、地点-地点（位于/毗邻/通道相连/包含于）；digHint 同步补充</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>提示词示例全是人物型关系（师徒/敌对/效忠/兄妹），模型天然不输出地点连线；校验层本身不限类型（from/to 只要命中白名单），改引导即可</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>十四、关系网：地点关系与线长（新增 · U9 批 · 2026-10-09 用户反馈）</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>U9-2</t>
+          <t>U9-1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>零 token 本地推导预连线</t>
+          <t>AI 补全关系支持地点关系</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>「AI 补全关系」面板新增「本地推导候选」：npc.location 与 regions.name 精确匹配→「驻地」；regions.desc/key 提到其他 region 名→「位于/毗邻」；勾选确认后写入</t>
+          <t>suggestRelations 提示词增加地点关系示例与明确要求：人物-地点（驻地/居住/把守/囚禁于）、地点-地点（位于/毗邻/通道相连/包含于）；digHint 同步补充</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>结构化字段里现成的关系不烧 token 也能高召回；与 AI 推断互补，且不受模型发挥影响</t>
+          <t>提示词示例全是人物型关系（师徒/敌对/效忠/兄妹），模型天然不输出地点连线；校验层本身不限类型（from/to 只要命中白名单），改引导即可</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2659,64 +2659,128 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>U9-3</t>
+          <t>U9-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>拉扯松手重锚自然长度</t>
+          <t>零 token 本地推导预连线</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>拖动松手时把被拖节点相关连线的 rest 更新为松手时实际长度（限幅 60~400px），拖近即真短、拖远即真长</t>
+          <t>点「AI 补全关系」即同时跑本地推导（零 token、不调上游）：npc/pc「所在位置」匹配地区名→「驻地」；regions「上级地区」→「位于」；desc/key 提及其他地区名→「毗邻」。候选带依据，与 AI 候选合并去重后同一预览弹窗勾选应用；AI 调用失败时本地候选仍可单独应用（经 IPC ai:relationsLocal）</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>relBuildRubber 把 rest 固定为「拖动开始时的长度」（app.js:9503），松手弹簧一律拉回原长→线长永远改不了，这就是「长度被固定」的直接原因</t>
+          <t>结构化字段里现成的关系不烧 token 也能高召回；与 AI 推断互补，且不受模型发挥影响</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>待开发</t>
+          <t>已完成（已验证）</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>U9-3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>拉扯松手重锚自然长度</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>拖动松手时把受影响连线的自然长度重锚为松手瞬间实际长度（relReanchorRests），再跑衰减收敛做微平衡——拖近即真短、拖远即真长，不再弹回拖动前长度</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>relBuildRubber 把 rest 固定为「拖动开始时的长度」（app.js:9503），松手弹簧一律拉回原长→线长永远改不了，这就是「长度被固定」的直接原因</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>已完成（已验证）</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>U9-4</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>「线长」滑杆与整理间距可调</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>关系网工具栏新增「线长」滑杆（80~360，默认 150，随设置落盘）：作为一键整理 relLocalLayout 的 rest 目标（替换 rad+26 硬编码）与 REL_REST_DEF 兜底，调整后对当前画布即时收敛</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>关系网工具栏新增「线长」滑杆（60~400，默认 150，随设置落盘）：作为一键整理 relLocalLayout 的 rest 目标（替换 rad+26 硬编码）与 REL_REST_DEF 兜底，调整后对当前画布即时收敛</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>relLocalLayout 的 rest=rad+26、REL_REST_DEF=150 全是硬编码，整理出的间距与回弹目标都无法由用户控制</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>待开发</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>已完成（已验证）</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>U9-5</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>关系提示词精调</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>①清单按类别分组注入（【人物】【地点】…分节），让模型按类型找地点对；②关系类型说明前置且给足地点示例（与 U9-1 配套）；③要求段措辞压缩，预算仍封顶（清单 14000/摘录 8000 字符）</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>清单 7 类实体混排 + 长要求段，模型容易只盯人物忽略地点；结构化分组可提升地点关系召回且不增 token</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>已完成（已验证）</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
